--- a/db/data/通識/1132通識.xlsx
+++ b/db/data/通識/1132通識.xlsx
@@ -1,409 +1,514 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrytseng/Downloads/credit-check-system/db/data/通識/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925CC15B-0B57-E849-A73D-09E4576043FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="14700" windowHeight="16280" xr2:uid="{1013D006-2E5F-3F4B-8783-93F541DEA095}"/>
+    <workbookView windowWidth="11051" windowHeight="9755"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159">
   <si>
     <t>code</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>credit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>course_name</t>
   </si>
   <si>
     <t>semester</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_core</t>
+  </si>
+  <si>
+    <t>090066001</t>
+  </si>
+  <si>
+    <t>看的方法（紀錄片）</t>
   </si>
   <si>
     <t>人文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090066001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>看的方法（紀錄片）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>090101001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>西歐歷史建築</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>090112001</t>
+  </si>
+  <si>
+    <t>自我探索與心理健康</t>
+  </si>
+  <si>
+    <t>090123001</t>
+  </si>
+  <si>
+    <t>舞蹈鑑賞</t>
+  </si>
+  <si>
+    <t>090120001</t>
+  </si>
+  <si>
+    <t>地方創生個案分析</t>
+  </si>
+  <si>
+    <t>社會</t>
+  </si>
+  <si>
+    <t>090014011</t>
+  </si>
+  <si>
+    <t>生物技術導論</t>
+  </si>
+  <si>
+    <t>自然</t>
+  </si>
+  <si>
+    <t>090020001</t>
+  </si>
+  <si>
+    <t>認識中醫藥</t>
+  </si>
+  <si>
+    <t>090025001</t>
+  </si>
+  <si>
+    <t>天氣與氣候</t>
+  </si>
+  <si>
+    <t>090033001</t>
+  </si>
+  <si>
+    <t>野生動物保育行銷</t>
+  </si>
+  <si>
+    <t>090043001</t>
+  </si>
+  <si>
+    <t>壓力與情緒管理</t>
+  </si>
+  <si>
+    <t>090044001</t>
+  </si>
+  <si>
+    <t>藥物使用與生活的關係</t>
+  </si>
+  <si>
+    <t>090060001</t>
+  </si>
+  <si>
+    <t>醫療與生活</t>
+  </si>
+  <si>
+    <t>090060011</t>
+  </si>
+  <si>
+    <t>090060021</t>
+  </si>
+  <si>
+    <t>090088001</t>
+  </si>
+  <si>
+    <t>預防醫學與校園健康</t>
+  </si>
+  <si>
+    <t>090104001</t>
+  </si>
+  <si>
+    <t>長期照護與健康產業發展</t>
+  </si>
+  <si>
+    <t>090106001</t>
+  </si>
+  <si>
+    <t>健康與生活</t>
+  </si>
+  <si>
+    <t>090109001</t>
+  </si>
+  <si>
+    <t>仰望星空探索宇宙</t>
+  </si>
+  <si>
+    <t>090111001</t>
+  </si>
+  <si>
+    <t>環境科學與環境保護</t>
+  </si>
+  <si>
+    <t>090114001</t>
+  </si>
+  <si>
+    <t>數位轉型的智權與風險管理</t>
+  </si>
+  <si>
+    <t>090122001</t>
+  </si>
+  <si>
+    <t>醫學新知與尖端研究</t>
+  </si>
+  <si>
+    <t>993015001</t>
+  </si>
+  <si>
+    <t>衛生保健</t>
+  </si>
+  <si>
+    <t>044022001</t>
+  </si>
+  <si>
+    <t>俄國文化與社會</t>
+  </si>
+  <si>
+    <t>人文、社會</t>
+  </si>
+  <si>
+    <t>044046001</t>
+  </si>
+  <si>
+    <t>自我．身體．文化</t>
+  </si>
+  <si>
+    <t>044049001</t>
+  </si>
+  <si>
+    <t>電影與國際關係</t>
+  </si>
+  <si>
+    <t>044075001</t>
+  </si>
+  <si>
+    <t>東南亞發展與治理</t>
+  </si>
+  <si>
+    <t>044085001</t>
+  </si>
+  <si>
+    <t>性別與文學理論入門</t>
+  </si>
+  <si>
+    <t>044101001</t>
+  </si>
+  <si>
+    <t>無所不在的人工智慧</t>
+  </si>
+  <si>
+    <t>人文、資訊</t>
+  </si>
+  <si>
+    <t>044110001</t>
+  </si>
+  <si>
+    <t>國際永續發展專題</t>
+  </si>
+  <si>
+    <t>044112001</t>
+  </si>
+  <si>
+    <t>園藝與生活</t>
+  </si>
+  <si>
+    <t>社會、自然</t>
+  </si>
+  <si>
+    <t>044115001</t>
+  </si>
+  <si>
+    <t>語言與認知神經科學概論</t>
+  </si>
+  <si>
+    <t>人文、自然</t>
+  </si>
+  <si>
+    <t>044119001</t>
+  </si>
+  <si>
+    <t>故事如何塑造法律</t>
+  </si>
+  <si>
+    <t>044120001</t>
+  </si>
+  <si>
+    <t>氣候變遷對社會韌性的挑戰</t>
   </si>
   <si>
     <t>090108001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>關於藝術的話題</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090112001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自我探索與心理健康</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090123001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>舞蹈鑑賞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社會</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090120001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地方創生個案分析</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090014011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生物技術導論</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090020001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>認識中醫藥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090025001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天氣與氣候</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090033001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野生動物保育行銷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090043001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>壓力與情緒管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090044001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藥物使用與生活的關係</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090060001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>醫療與生活</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090060011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090060021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090088001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>預防醫學與校園健康</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090104001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>長期照護與健康產業發展</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090106001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>健康與生活</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090109001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仰望星空探索宇宙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090111001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>環境科學與環境保護</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090114001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>數位轉型的智權與風險管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>090122001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>醫學新知與尖端研究</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>993015001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>衛生保健</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044022001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>俄國文化與社會</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044046001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自我．身體．文化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人文、社會</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044049001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>電影與國際關係</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044075001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>東南亞發展與治理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044085001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>性別與文學理論入門</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044101001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>無所不在的人工智慧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044110001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>國際永續發展專題</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人文、資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044112001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>園藝與生活</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社會、自然</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044115001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>語言與認知神經科學概論</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人文、自然</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044119001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故事如何塑造法律</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>044120001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>氣候變遷對社會韌性的挑戰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>090115001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>資訊素養與倫理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>自然、資訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>090118001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>幸福學</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>090119001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>三貓生態食農傳播實踐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>course_name</t>
-  </si>
-  <si>
-    <t>is_core</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>No</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>041135001</t>
+  </si>
+  <si>
+    <t>西方文學經典與人文思維</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>041195001</t>
+  </si>
+  <si>
+    <t>藝術與當代社會</t>
+  </si>
+  <si>
+    <t>041195011</t>
+  </si>
+  <si>
+    <t>041100001</t>
+  </si>
+  <si>
+    <t>生命價值與哲學思惟</t>
+  </si>
+  <si>
+    <t>041100031</t>
+  </si>
+  <si>
+    <t>041123001</t>
+  </si>
+  <si>
+    <t>生命探索與宗教文化</t>
+  </si>
+  <si>
+    <t>041123011</t>
+  </si>
+  <si>
+    <t>041099011</t>
+  </si>
+  <si>
+    <t>文明發展與歷史思惟</t>
+  </si>
+  <si>
+    <t>041099041</t>
+  </si>
+  <si>
+    <t>041133011</t>
+  </si>
+  <si>
+    <t>近代臺灣歷史與人物</t>
+  </si>
+  <si>
+    <t>041177001</t>
+  </si>
+  <si>
+    <t>語言的人文與科學</t>
+  </si>
+  <si>
+    <t>041177011</t>
+  </si>
+  <si>
+    <t>041177021</t>
+  </si>
+  <si>
+    <t>042112101</t>
+  </si>
+  <si>
+    <t>臺灣政治</t>
+  </si>
+  <si>
+    <t>042137001</t>
+  </si>
+  <si>
+    <t>法學素養</t>
+  </si>
+  <si>
+    <t>042137011</t>
+  </si>
+  <si>
+    <t>042139021</t>
+  </si>
+  <si>
+    <t>認識智慧財產權</t>
+  </si>
+  <si>
+    <t>042116011</t>
+  </si>
+  <si>
+    <t>生活中的經濟學</t>
+  </si>
+  <si>
+    <t>042116041</t>
+  </si>
+  <si>
+    <t>042133001</t>
+  </si>
+  <si>
+    <t>社會學動動腦</t>
+  </si>
+  <si>
+    <t>042133011</t>
+  </si>
+  <si>
+    <t>042181001</t>
+  </si>
+  <si>
+    <t>教育探索與自我學習</t>
+  </si>
+  <si>
+    <t>042181011</t>
+  </si>
+  <si>
+    <t>042181021</t>
+  </si>
+  <si>
+    <t>042142001</t>
+  </si>
+  <si>
+    <t>環視全球－挑戰國際視野</t>
+  </si>
+  <si>
+    <t>042142021</t>
+  </si>
+  <si>
+    <t>042156001</t>
+  </si>
+  <si>
+    <t>中國大陸概論</t>
+  </si>
+  <si>
+    <t>042156021</t>
+  </si>
+  <si>
+    <t>042156031</t>
+  </si>
+  <si>
+    <t>042156051</t>
+  </si>
+  <si>
+    <t>043042001</t>
+  </si>
+  <si>
+    <t>醫病風險數據與醫療（照護）管理</t>
+  </si>
+  <si>
+    <t>043024001</t>
+  </si>
+  <si>
+    <t>物理學史與人類文明</t>
+  </si>
+  <si>
+    <t>043016001</t>
+  </si>
+  <si>
+    <t>生活中的生命科學</t>
+  </si>
+  <si>
+    <t>043016011</t>
+  </si>
+  <si>
+    <t>043025001</t>
+  </si>
+  <si>
+    <t>大腦與我</t>
+  </si>
+  <si>
+    <t>043025011</t>
+  </si>
+  <si>
+    <t>043027001</t>
+  </si>
+  <si>
+    <t>科技與人文社會</t>
+  </si>
+  <si>
+    <t>046006021</t>
+  </si>
+  <si>
+    <t>計算思維與人工智慧</t>
+  </si>
+  <si>
+    <t>資訊</t>
+  </si>
+  <si>
+    <t>046006031</t>
+  </si>
+  <si>
+    <t>046009001</t>
+  </si>
+  <si>
+    <t>生成式人工智慧時代的生活紀實</t>
+  </si>
+  <si>
+    <t>046001001</t>
+  </si>
+  <si>
+    <t>程式設計概論</t>
+  </si>
+  <si>
+    <t>046001011</t>
+  </si>
+  <si>
+    <t>046001031</t>
+  </si>
+  <si>
+    <t>046001041</t>
+  </si>
+  <si>
+    <t>046001021</t>
+  </si>
+  <si>
+    <t>046003011</t>
+  </si>
+  <si>
+    <t>人工智慧與數位人文</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -412,7 +517,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -420,19 +524,400 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="PMingLiU"/>
-      <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF333333"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -442,58 +927,401 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
+    <cellStyle name="20% - 輔色2" xfId="2" builtinId="34"/>
+    <cellStyle name="千分位[0]" xfId="3" builtinId="6"/>
+    <cellStyle name="千分位" xfId="4" builtinId="3"/>
+    <cellStyle name="20% - 輔色1" xfId="5" builtinId="30"/>
+    <cellStyle name="貨幣" xfId="6" builtinId="4"/>
+    <cellStyle name="備註" xfId="7" builtinId="10"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="8" builtinId="9"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="20% - 輔色5" xfId="10" builtinId="46"/>
+    <cellStyle name="40% - 輔色3" xfId="11" builtinId="39"/>
+    <cellStyle name="60% - 輔色1" xfId="12" builtinId="32"/>
+    <cellStyle name="貨幣[0]" xfId="13" builtinId="7"/>
+    <cellStyle name="警告文字" xfId="14" builtinId="11"/>
+    <cellStyle name="標題" xfId="15" builtinId="15"/>
+    <cellStyle name="說明文字" xfId="16" builtinId="53"/>
+    <cellStyle name="40% - 輔色6" xfId="17" builtinId="51"/>
+    <cellStyle name="60% - 輔色4" xfId="18" builtinId="44"/>
+    <cellStyle name="標題 1" xfId="19" builtinId="16"/>
+    <cellStyle name="60% - 輔色5" xfId="20" builtinId="48"/>
+    <cellStyle name="標題 2" xfId="21" builtinId="17"/>
+    <cellStyle name="60% - 輔色6" xfId="22" builtinId="52"/>
+    <cellStyle name="標題 3" xfId="23" builtinId="18"/>
+    <cellStyle name="標題 4" xfId="24" builtinId="19"/>
+    <cellStyle name="好" xfId="25" builtinId="26"/>
+    <cellStyle name="輸入" xfId="26" builtinId="20"/>
+    <cellStyle name="輸出" xfId="27" builtinId="21"/>
+    <cellStyle name="計算方式" xfId="28" builtinId="22"/>
+    <cellStyle name="檢查儲存格" xfId="29" builtinId="23"/>
+    <cellStyle name="連結的儲存格" xfId="30" builtinId="24"/>
+    <cellStyle name="加總" xfId="31" builtinId="25"/>
+    <cellStyle name="壞" xfId="32" builtinId="27"/>
+    <cellStyle name="中性" xfId="33" builtinId="28"/>
+    <cellStyle name="輔色1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 輔色3" xfId="35" builtinId="38"/>
+    <cellStyle name="40% - 輔色1" xfId="36" builtinId="31"/>
+    <cellStyle name="輔色2" xfId="37" builtinId="33"/>
+    <cellStyle name="20% - 輔色4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 輔色2" xfId="39" builtinId="35"/>
+    <cellStyle name="20% - 輔色6" xfId="40" builtinId="50"/>
+    <cellStyle name="40% - 輔色4" xfId="41" builtinId="43"/>
+    <cellStyle name="60% - 輔色2" xfId="42" builtinId="36"/>
+    <cellStyle name="輔色3" xfId="43" builtinId="37"/>
+    <cellStyle name="40% - 輔色5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 輔色3" xfId="45" builtinId="40"/>
+    <cellStyle name="輔色4" xfId="46" builtinId="41"/>
+    <cellStyle name="輔色5" xfId="47" builtinId="45"/>
+    <cellStyle name="輔色6" xfId="48" builtinId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
 </file>
 
@@ -540,7 +1368,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -573,26 +1401,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -625,23 +1436,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -783,125 +1577,121 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13A318A-B106-4948-9665-726D23CEEE7E}">
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="10.8333333333333" style="2"/>
+    <col min="3" max="3" width="20.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>85</v>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
+      <c r="A2" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>1132</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>1132</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
-        <v>1132</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
+      <c r="A4" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>1132</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
+      <c r="A5" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1132</v>
       </c>
       <c r="E5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B6">
@@ -914,14 +1704,14 @@
         <v>1132</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B7">
@@ -934,634 +1724,1574 @@
         <v>1132</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
+      <c r="A8" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>1132</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>23</v>
+      <c r="A9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>1132</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>25</v>
+      <c r="A10" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>1132</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>27</v>
+      <c r="A11" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>1132</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>29</v>
+      <c r="A12" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12">
         <v>1132</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>31</v>
+      <c r="A13" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>1132</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>33</v>
+      <c r="A14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>1132</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>34</v>
+      <c r="A15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>1132</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>35</v>
+      <c r="A16" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>1132</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>37</v>
+      <c r="A17" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>1132</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>39</v>
+      <c r="A18" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>1132</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>41</v>
+      <c r="A19" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19">
         <v>1132</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="4" t="s">
-        <v>43</v>
+      <c r="A20" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20">
         <v>1132</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="4" t="s">
-        <v>45</v>
+      <c r="A21" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>1132</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="4" t="s">
-        <v>47</v>
+      <c r="A22" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>1132</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="4" t="s">
-        <v>49</v>
+      <c r="A23" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23">
         <v>1132</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="4" t="s">
-        <v>51</v>
+      <c r="A24" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>1132</v>
       </c>
       <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25">
+        <v>1132</v>
+      </c>
+      <c r="E25" t="s">
         <v>54</v>
       </c>
-      <c r="D25">
-        <v>1132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>55</v>
-      </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="4" t="s">
-        <v>56</v>
+      <c r="A26" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>1132</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="4" t="s">
-        <v>58</v>
+      <c r="A27" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D27">
         <v>1132</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="4" t="s">
-        <v>60</v>
+      <c r="A28" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28">
         <v>1132</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="4" t="s">
-        <v>62</v>
+      <c r="A29" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29">
         <v>1132</v>
       </c>
       <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D30">
         <v>1132</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="4" t="s">
-        <v>67</v>
+      <c r="A31" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D31">
         <v>1132</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>70</v>
+      <c r="A32" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D32">
         <v>1132</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>73</v>
+      <c r="A33" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33">
         <v>1132</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="4" t="s">
-        <v>75</v>
+      <c r="A34" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D34">
         <v>1132</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="4" t="s">
-        <v>9</v>
+      <c r="A35" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D35">
         <v>1132</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F35" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="4" t="s">
-        <v>77</v>
+      <c r="A36" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D36">
         <v>1132</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="4" t="s">
-        <v>80</v>
+      <c r="A37" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D37">
         <v>1132</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="4" t="s">
-        <v>82</v>
+      <c r="A38" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D38">
         <v>1132</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39">
+        <v>1132</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40">
+        <v>1132</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41">
+        <v>1132</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="10">
+        <v>3</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42">
+        <v>1132</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="10">
+        <v>3</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43">
+        <v>1132</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="10">
+        <v>3</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44">
+        <v>1132</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="10">
+        <v>3</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45">
+        <v>1132</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46">
+        <v>1132</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47">
+        <v>1132</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="13">
+        <v>3</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48">
+        <v>1132</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49">
+        <v>1132</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="13">
+        <v>3</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50">
+        <v>1132</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51">
+        <v>1132</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="11">
+        <v>3</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52">
+        <v>1132</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="14">
+        <v>3</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53">
+        <v>1132</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="14">
+        <v>3</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54">
+        <v>1132</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="14">
+        <v>3</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55">
+        <v>1132</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="17">
+        <v>3</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56">
+        <v>1132</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" s="17">
+        <v>3</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57">
+        <v>1132</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="17">
+        <v>3</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D58">
+        <v>1132</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" s="17">
+        <v>3</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D59">
+        <v>1132</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="17">
+        <v>3</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60">
+        <v>1132</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="17">
+        <v>3</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61">
+        <v>1132</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="17">
+        <v>3</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62">
+        <v>1132</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" s="20">
+        <v>3</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63">
+        <v>1132</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="20">
+        <v>3</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64">
+        <v>1132</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="20">
+        <v>3</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D65">
+        <v>1132</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="20">
+        <v>3</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66">
+        <v>1132</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="20">
+        <v>3</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D67">
+        <v>1132</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="20">
+        <v>3</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D68">
+        <v>1132</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:6">
+      <c r="A69" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" s="22">
+        <v>2</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69">
+        <v>1132</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="24">
+        <v>3</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70">
+        <v>1132</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D71">
+        <v>1132</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
+      </c>
+      <c r="C72" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72">
+        <v>1132</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73">
+        <v>1132</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" s="1">
+        <v>3</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D74">
+        <v>1132</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="28">
+        <v>3</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75">
+        <v>1132</v>
+      </c>
+      <c r="E75" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" s="24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="1">
+        <v>3</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76">
+        <v>1132</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F76" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77">
+        <v>1132</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F77" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B78" s="1">
+        <v>3</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D78">
+        <v>1132</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F78" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79">
+        <v>1132</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F79" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" s="31">
+        <v>3</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D80">
+        <v>1131</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="31">
+        <v>3</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D81">
+        <v>1131</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" s="31">
+        <v>3</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D82">
+        <v>1131</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" s="31">
+        <v>3</v>
+      </c>
+      <c r="C83" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D83">
+        <v>1131</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F83" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" s="31">
+        <v>3</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84">
+        <v>1131</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F84" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" s="31">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>158</v>
+      </c>
+      <c r="D85">
+        <v>1131</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>